--- a/education_surveys/045_student_technological_readiness_assessment--education_surveys.xlsx
+++ b/education_surveys/045_student_technological_readiness_assessment--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'text':_'basic'}</t>
+          <t>basic</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'text': 'Basic'}</t>
+          <t>Basic</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'text':_'intermediate'}</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'text': 'Intermediate'}</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'text':_'advanced'}</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'text': 'Advanced'}</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'text':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'text': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'text':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'text': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'text':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'text': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'text':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'text': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'text':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'text': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'text':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'text': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'text':_'no_issues'}</t>
+          <t>no_issues</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'text': 'No Issues'}</t>
+          <t>No Issues</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'text':_'minor_issues'}</t>
+          <t>minor_issues</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'text': 'Minor Issues'}</t>
+          <t>Minor Issues</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'text':_'major_issues'}</t>
+          <t>major_issues</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'text': 'Major Issues'}</t>
+          <t>Major Issues</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'text':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'text': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'text':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'text': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'text':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'text': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'text':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'text': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'text':_'mobile_phone'}</t>
+          <t>mobile_phone</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'text': 'Mobile Phone'}</t>
+          <t>Mobile Phone</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'text':_'desktop_computer'}</t>
+          <t>desktop_computer</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'text': 'Desktop Computer'}</t>
+          <t>Desktop Computer</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'text':_'laptop'}</t>
+          <t>laptop</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'text': 'Laptop'}</t>
+          <t>Laptop</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'text':_'tablet'}</t>
+          <t>tablet</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'text': 'Tablet'}</t>
+          <t>Tablet</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'text':_'new'}</t>
+          <t>new</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'text': 'New'}</t>
+          <t>New</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'text':_'used'}</t>
+          <t>used</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'text': 'Used'}</t>
+          <t>Used</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'text':_'refurbished'}</t>
+          <t>refurbished</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'text': 'Refurbished'}</t>
+          <t>Refurbished</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'text':_'fast'}</t>
+          <t>fast</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'text': 'Fast'}</t>
+          <t>Fast</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'text':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'text': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'text':_'slow'}</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'text': 'Slow'}</t>
+          <t>Slow</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'text':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'text': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'text':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'text': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'text':_'hardware_issues'}</t>
+          <t>hardware_issues</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'text': 'Hardware Issues'}</t>
+          <t>Hardware Issues</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'text':_'software_issues'}</t>
+          <t>software_issues</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'text': 'Software Issues'}</t>
+          <t>Software Issues</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'text':_'connection_issues'}</t>
+          <t>connection_issues</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'text': 'Connection Issues'}</t>
+          <t>Connection Issues</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'text':_'slow_speed'}</t>
+          <t>slow_speed</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'text': 'Slow Speed'}</t>
+          <t>Slow Speed</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'text':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'text': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1777,12 +1777,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'text':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'text': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'text':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'text': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'text':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'text': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'text':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'text': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1845,12 +1845,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'text':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'text': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1862,12 +1862,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'text':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'text': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1879,12 +1879,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'text':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'text': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'text':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'text': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1913,12 +1913,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'text':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'text': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1930,12 +1930,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>{'text':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>{'text': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1947,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>{'text':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>{'text': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1964,12 +1964,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>{'text':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>{'text': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>{'text':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>{'text': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1998,12 +1998,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>{'text':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>{'text': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2015,12 +2015,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>{'text':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>{'text': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2032,12 +2032,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>{'text':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>{'text': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2049,12 +2049,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>{'text':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>{'text': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -2066,12 +2066,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>{'text':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>{'text': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -2083,12 +2083,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>{'text':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>{'text': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>{'text':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>{'text': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
